--- a/evac_by_zip/evac_by_zip_2026-09-02.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-09-02.xlsx
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>177</v>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
@@ -1032,72 +1032,74 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Level 2</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>97862</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="B16" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Level 1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Level 2</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>No named fire</t>
         </is>
@@ -1110,16 +1112,16 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>1069</v>
+        <v>1133</v>
       </c>
       <c r="C18" s="14" t="n">
-        <v>342</v>
+        <v>277</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>48</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="19">
@@ -1148,16 +1150,16 @@
         </is>
       </c>
       <c r="B20" s="18" t="n">
-        <v>1227</v>
+        <v>1291</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>351</v>
+        <v>286</v>
       </c>
       <c r="D20" s="18" t="n">
         <v>76</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>1654</v>
+        <v>1653</v>
       </c>
     </row>
   </sheetData>
@@ -1175,7 +1177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1799,7 +1801,7 @@
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-121-B</t>
+          <t>US-OR-UMA-UMC-149-B</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
@@ -1819,7 +1821,7 @@
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="G19" s="25" t="n">
@@ -1827,38 +1829,38 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>97886</t>
-        </is>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-149-B</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>1</v>
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>97877</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-McCullyForkHeadwaters</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Baker, Grant</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1869,7 +1871,7 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-McCullyForkHeadwaters</t>
+          <t>US-OR-GRA-GRN-043-N</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -1889,11 +1891,11 @@
       </c>
       <c r="F21" s="21" t="inlineStr">
         <is>
-          <t>92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G21" s="21" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1904,7 +1906,7 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-043-N</t>
+          <t>US-OR-GRA-GRN-043-L</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -1939,7 +1941,7 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-043-L</t>
+          <t>US-OR-BAK-BAB-1246</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -1959,11 +1961,11 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G23" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1974,7 +1976,7 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1246</t>
+          <t>US-OR-GRA-GRN-043-E</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -1994,7 +1996,7 @@
       </c>
       <c r="F24" s="21" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G24" s="21" t="n">
@@ -2009,7 +2011,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-043-E</t>
+          <t>US-OR-BAK-BAB-1247</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -2029,7 +2031,7 @@
       </c>
       <c r="F25" s="21" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G25" s="21" t="n">
@@ -2044,7 +2046,7 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1247</t>
+          <t>US-OR-BAK-BAB-1347-B</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -2064,7 +2066,7 @@
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>21%</t>
         </is>
       </c>
       <c r="G26" s="21" t="n">
@@ -2072,38 +2074,38 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>97877</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1347-B</t>
-        </is>
-      </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-GRA-GRN-019-C</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
         <is>
           <t>Baker, Grant</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>21%</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="n">
-        <v>1</v>
+      <c r="E27" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F27" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G27" s="23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2114,7 +2116,7 @@
       </c>
       <c r="B28" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-019-C</t>
+          <t>US-OR-GRA-GRN-019-E</t>
         </is>
       </c>
       <c r="C28" s="24" t="inlineStr">
@@ -2134,7 +2136,7 @@
       </c>
       <c r="F28" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="G28" s="23" t="n">
@@ -2149,7 +2151,7 @@
       </c>
       <c r="B29" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-019-E</t>
+          <t>US-OR-BAK-SMT-636</t>
         </is>
       </c>
       <c r="C29" s="24" t="inlineStr">
@@ -2169,11 +2171,11 @@
       </c>
       <c r="F29" s="23" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="G29" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2184,7 +2186,7 @@
       </c>
       <c r="B30" s="24" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-636</t>
+          <t>US-OR-GRA-GRN-043-H</t>
         </is>
       </c>
       <c r="C30" s="24" t="inlineStr">
@@ -2204,7 +2206,7 @@
       </c>
       <c r="F30" s="23" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G30" s="23" t="n">
@@ -2212,38 +2214,38 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>97877</t>
         </is>
       </c>
-      <c r="B31" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-043-H</t>
-        </is>
-      </c>
-      <c r="C31" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D31" s="24" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-600</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
         <is>
           <t>Baker, Grant</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F31" s="23" t="inlineStr">
-        <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="G31" s="23" t="n">
-        <v>1</v>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="32">
@@ -2254,7 +2256,7 @@
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-600</t>
+          <t>US-OR-BAK-SMT-610</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
@@ -2278,7 +2280,7 @@
         </is>
       </c>
       <c r="G32" s="25" t="n">
-        <v>115</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
@@ -2289,7 +2291,7 @@
       </c>
       <c r="B33" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-610</t>
+          <t>US-OR-BAK-SMT-632</t>
         </is>
       </c>
       <c r="C33" s="26" t="inlineStr">
@@ -2309,81 +2311,81 @@
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="G33" s="25" t="n">
-        <v>102</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B34" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-632</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E34" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F34" s="25" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>22</v>
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140618N</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="21" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140624S</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="n">
-        <v>29</v>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F35" s="23" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2394,7 +2396,7 @@
       </c>
       <c r="B36" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624S</t>
+          <t>US-OR-UMA-UMC-1406024A</t>
         </is>
       </c>
       <c r="C36" s="24" t="inlineStr">
@@ -2414,7 +2416,7 @@
       </c>
       <c r="F36" s="23" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G36" s="23" t="n">
@@ -2422,38 +2424,38 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B37" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D37" s="24" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140624N-B</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E37" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F37" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>1</v>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -2464,7 +2466,7 @@
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
+          <t>US-OR-UNI-UCO-1497</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
@@ -2484,11 +2486,11 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G38" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2499,7 +2501,7 @@
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1497</t>
+          <t>US-OR-UNI-UCO-1505</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
@@ -2519,7 +2521,7 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G39" s="25" t="n">
@@ -2534,7 +2536,7 @@
       </c>
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1505</t>
+          <t>US-OR-UNI-UCO-1513</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
@@ -2554,7 +2556,7 @@
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G40" s="25" t="n">
@@ -2569,7 +2571,7 @@
       </c>
       <c r="B41" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1513</t>
+          <t>US-OR-UMA-UMC-1406030-A</t>
         </is>
       </c>
       <c r="C41" s="26" t="inlineStr">
@@ -2589,7 +2591,7 @@
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G41" s="25" t="n">
@@ -2604,7 +2606,7 @@
       </c>
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>US-OR-UNI-UCO-1495</t>
         </is>
       </c>
       <c r="C42" s="26" t="inlineStr">
@@ -2632,37 +2634,37 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B43" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1495</t>
-        </is>
-      </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D43" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E43" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F43" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G43" s="25" t="n">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1119-B</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D43" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2674,7 +2676,7 @@
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1119-B</t>
+          <t>US-OR-BAK-BAB-1247</t>
         </is>
       </c>
       <c r="C44" s="22" t="inlineStr">
@@ -2694,7 +2696,7 @@
       </c>
       <c r="F44" s="21" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G44" s="21" t="n">
@@ -2709,7 +2711,7 @@
       </c>
       <c r="B45" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1247</t>
+          <t>US-OR-BAK-BAB-1246</t>
         </is>
       </c>
       <c r="C45" s="22" t="inlineStr">
@@ -2729,7 +2731,7 @@
       </c>
       <c r="F45" s="21" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G45" s="21" t="n">
@@ -2737,73 +2739,73 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="21" t="inlineStr">
+      <c r="A46" s="23" t="inlineStr">
         <is>
           <t>97814</t>
         </is>
       </c>
-      <c r="B46" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1246</t>
-        </is>
-      </c>
-      <c r="C46" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D46" s="22" t="inlineStr">
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-636</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E46" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F46" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G46" s="21" t="n">
+      <c r="E46" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F46" s="23" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>97814</t>
         </is>
       </c>
-      <c r="B47" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-636</t>
-        </is>
-      </c>
-      <c r="C47" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1252</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E47" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F47" s="23" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G47" s="23" t="n">
-        <v>1</v>
+      <c r="E47" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G47" s="25" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="48">
@@ -2814,7 +2816,7 @@
       </c>
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1252</t>
+          <t>US-OR-BAK-SMT-610</t>
         </is>
       </c>
       <c r="C48" s="26" t="inlineStr">
@@ -2834,11 +2836,11 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G48" s="25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -2849,7 +2851,7 @@
       </c>
       <c r="B49" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-610</t>
+          <t>US-OR-BAK-SMT-600</t>
         </is>
       </c>
       <c r="C49" s="26" t="inlineStr">
@@ -2884,7 +2886,7 @@
       </c>
       <c r="B50" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-600</t>
+          <t>US-OR-BAK-BAB-1242</t>
         </is>
       </c>
       <c r="C50" s="26" t="inlineStr">
@@ -2904,7 +2906,7 @@
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G50" s="25" t="n">
@@ -2912,73 +2914,73 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B51" s="26" t="inlineStr">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>97833</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1119-B</t>
+        </is>
+      </c>
+      <c r="C51" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D51" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G51" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="25" t="inlineStr">
+        <is>
+          <t>97833</t>
+        </is>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
         <is>
           <t>US-OR-BAK-BAB-1242</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D51" s="26" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D52" s="26" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E51" s="25" t="inlineStr">
+      <c r="E52" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F51" s="25" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G51" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="21" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B52" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1119-B</t>
-        </is>
-      </c>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D52" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E52" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F52" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G52" s="21" t="n">
-        <v>1</v>
+      <c r="F52" s="25" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="G52" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -2989,7 +2991,7 @@
       </c>
       <c r="B53" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1242</t>
+          <t>US-OR-BAK-BAB-1252</t>
         </is>
       </c>
       <c r="C53" s="26" t="inlineStr">
@@ -3009,67 +3011,67 @@
       </c>
       <c r="F53" s="25" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G53" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="25" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B54" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1252</t>
-        </is>
-      </c>
-      <c r="C54" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D54" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E54" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F54" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G54" s="25" t="n">
-        <v>1</v>
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F54" s="21" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G54" s="21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>NF 27</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C55" s="22" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D55" s="22" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E55" s="21" t="inlineStr">
@@ -3079,32 +3081,32 @@
       </c>
       <c r="F55" s="21" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G55" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>97023</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>NF 27</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D56" s="22" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E56" s="21" t="inlineStr">
@@ -3114,7 +3116,7 @@
       </c>
       <c r="F56" s="21" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G56" s="21" t="n">
@@ -3124,22 +3126,22 @@
     <row r="57">
       <c r="A57" s="21" t="inlineStr">
         <is>
-          <t>97063</t>
+          <t>97358</t>
         </is>
       </c>
       <c r="B57" s="22" t="inlineStr">
         <is>
-          <t>NF 27</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C57" s="22" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D57" s="22" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E57" s="21" t="inlineStr">
@@ -3149,7 +3151,7 @@
       </c>
       <c r="F57" s="21" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G57" s="21" t="n">
@@ -3157,38 +3159,38 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="21" t="inlineStr">
-        <is>
-          <t>97358</t>
-        </is>
-      </c>
-      <c r="B58" s="22" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C58" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D58" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E58" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F58" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G58" s="21" t="n">
-        <v>1</v>
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E58" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F58" s="23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G58" s="23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3199,7 +3201,7 @@
       </c>
       <c r="B59" s="24" t="inlineStr">
         <is>
-          <t>Elk Mountain</t>
+          <t>Mill Creek Buttes</t>
         </is>
       </c>
       <c r="C59" s="24" t="inlineStr">
@@ -3219,46 +3221,46 @@
       </c>
       <c r="F59" s="23" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G59" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="23" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B60" s="24" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C60" s="24" t="inlineStr">
+      <c r="B60" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur North</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D60" s="24" t="inlineStr">
+      <c r="D60" s="26" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E60" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F60" s="23" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G60" s="23" t="n">
-        <v>2</v>
+      <c r="E60" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F60" s="25" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G60" s="25" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="61">
@@ -3269,7 +3271,7 @@
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>Cooper Spur North</t>
+          <t>Cooper Spur South</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
@@ -3289,11 +3291,11 @@
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G61" s="25" t="n">
-        <v>158</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62">
@@ -3304,7 +3306,7 @@
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>Cooper Spur South</t>
+          <t>Gibson Prairie</t>
         </is>
       </c>
       <c r="C62" s="26" t="inlineStr">
@@ -3324,11 +3326,11 @@
       </c>
       <c r="F62" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G62" s="25" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -3339,7 +3341,7 @@
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>Gibson Prairie</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C63" s="26" t="inlineStr">
@@ -3359,46 +3361,46 @@
       </c>
       <c r="F63" s="25" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G63" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B64" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E64" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F64" s="25" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="G64" s="25" t="n">
-        <v>1</v>
+      <c r="A64" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406017-A</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E64" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F64" s="23" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G64" s="23" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="65">
@@ -3409,7 +3411,7 @@
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>US-OR-UMA-UMC-1406053-C</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -3429,11 +3431,11 @@
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G65" s="23" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66">
@@ -3444,7 +3446,7 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406053-C</t>
+          <t>US-OR-UMA-UMC-1406015-E</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -3468,7 +3470,7 @@
         </is>
       </c>
       <c r="G66" s="23" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
@@ -3479,7 +3481,7 @@
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-E</t>
+          <t>US-OR-UMA-UMC-153</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -3499,11 +3501,11 @@
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G67" s="23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
@@ -3514,7 +3516,7 @@
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-153</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -3534,11 +3536,11 @@
       </c>
       <c r="F68" s="23" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G68" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
@@ -3549,7 +3551,7 @@
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-UMA-UMC-1406015G</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -3569,11 +3571,11 @@
       </c>
       <c r="F69" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G69" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -3584,7 +3586,7 @@
       </c>
       <c r="B70" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015G</t>
+          <t>US-OR-UMA-UMC-1406015-C</t>
         </is>
       </c>
       <c r="C70" s="24" t="inlineStr">
@@ -3608,7 +3610,7 @@
         </is>
       </c>
       <c r="G70" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -3619,7 +3621,7 @@
       </c>
       <c r="B71" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-UMA-UMC-1406053-B</t>
         </is>
       </c>
       <c r="C71" s="24" t="inlineStr">
@@ -3643,42 +3645,42 @@
         </is>
       </c>
       <c r="G71" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="23" t="inlineStr">
+      <c r="A72" s="25" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B72" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
-        </is>
-      </c>
-      <c r="C72" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D72" s="24" t="inlineStr">
+      <c r="B72" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-C</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D72" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E72" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F72" s="23" t="inlineStr">
+      <c r="E72" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F72" s="25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G72" s="23" t="n">
-        <v>1</v>
+      <c r="G72" s="25" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="73">
@@ -3689,7 +3691,7 @@
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-C</t>
+          <t>US-OR-UMA-UMC-215-E</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
@@ -3713,7 +3715,7 @@
         </is>
       </c>
       <c r="G73" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74">
@@ -3724,7 +3726,7 @@
       </c>
       <c r="B74" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-E</t>
+          <t>US-OR-UMA-UMC-215-D</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
@@ -3748,7 +3750,7 @@
         </is>
       </c>
       <c r="G74" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
@@ -3759,7 +3761,7 @@
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-D</t>
+          <t>US-OR-UMA-UMC-215-F</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
@@ -3783,7 +3785,7 @@
         </is>
       </c>
       <c r="G75" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -3794,7 +3796,7 @@
       </c>
       <c r="B76" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-F</t>
+          <t>US-OR-UMA-UMC-151-D</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
@@ -3814,7 +3816,7 @@
       </c>
       <c r="F76" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G76" s="25" t="n">
@@ -3829,7 +3831,7 @@
       </c>
       <c r="B77" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-UMA-UMC-149-B</t>
         </is>
       </c>
       <c r="C77" s="26" t="inlineStr">
@@ -3849,11 +3851,11 @@
       </c>
       <c r="F77" s="25" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="G77" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3864,7 +3866,7 @@
       </c>
       <c r="B78" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-149-B</t>
+          <t>US-OR-UMA-UMC-155-B</t>
         </is>
       </c>
       <c r="C78" s="26" t="inlineStr">
@@ -3884,7 +3886,7 @@
       </c>
       <c r="F78" s="25" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G78" s="25" t="n">
@@ -3892,143 +3894,143 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="25" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B79" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-155-B</t>
-        </is>
-      </c>
-      <c r="C79" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D79" s="26" t="inlineStr">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406043-C</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E79" s="25" t="inlineStr">
+      <c r="E79" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F79" s="23" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G79" s="23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="25" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B80" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C80" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D80" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E80" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F79" s="25" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G79" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="23" t="inlineStr">
+      <c r="F80" s="25" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G80" s="25" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="25" t="inlineStr">
         <is>
           <t>99362</t>
         </is>
       </c>
-      <c r="B80" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C80" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D80" s="24" t="inlineStr">
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-032</t>
+        </is>
+      </c>
+      <c r="C81" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D81" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E80" s="23" t="inlineStr">
+      <c r="E81" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F81" s="25" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="G81" s="25" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F80" s="23" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G80" s="23" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="23" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B81" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
-        </is>
-      </c>
-      <c r="C81" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D81" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E81" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F81" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G81" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B82" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E82" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F82" s="25" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G82" s="25" t="n">
-        <v>22</v>
+      <c r="F82" s="23" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G82" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="83">
@@ -4039,7 +4041,7 @@
       </c>
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1435</t>
+          <t>US-OR-UNI-UCO-1450</t>
         </is>
       </c>
       <c r="C83" s="24" t="inlineStr">
@@ -4059,46 +4061,46 @@
       </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G83" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="23" t="inlineStr">
+      <c r="A84" s="25" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B84" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D84" s="24" t="inlineStr">
+      <c r="B84" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1421</t>
+        </is>
+      </c>
+      <c r="C84" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D84" s="26" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E84" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F84" s="23" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G84" s="23" t="n">
-        <v>1</v>
+      <c r="E84" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F84" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G84" s="25" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="85">
@@ -4109,7 +4111,7 @@
       </c>
       <c r="B85" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-UNI-UCO-1436</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
@@ -4133,7 +4135,7 @@
         </is>
       </c>
       <c r="G85" s="25" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -4144,7 +4146,7 @@
       </c>
       <c r="B86" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1436</t>
+          <t>US-OR-UNI-UCO-1437</t>
         </is>
       </c>
       <c r="C86" s="26" t="inlineStr">
@@ -4179,7 +4181,7 @@
       </c>
       <c r="B87" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C87" s="26" t="inlineStr">
@@ -4199,7 +4201,7 @@
       </c>
       <c r="F87" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G87" s="25" t="n">
@@ -4207,72 +4209,72 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="25" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B88" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1438</t>
-        </is>
-      </c>
-      <c r="C88" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D88" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E88" s="25" t="inlineStr">
+      <c r="A88" s="23" t="inlineStr">
+        <is>
+          <t>97859</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406007-B</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E88" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F88" s="23" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G88" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B89" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C89" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D89" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E89" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F88" s="25" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G88" s="25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="23" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B89" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C89" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D89" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E89" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F89" s="23" t="inlineStr">
+      <c r="F89" s="25" t="inlineStr">
         <is>
           <t>12%</t>
         </is>
       </c>
-      <c r="G89" s="23" t="n">
+      <c r="G89" s="25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -4314,22 +4316,22 @@
     <row r="91">
       <c r="A91" s="25" t="inlineStr">
         <is>
-          <t>97862</t>
+          <t>97028</t>
         </is>
       </c>
       <c r="B91" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-121-B</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C91" s="26" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D91" s="26" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Hood River</t>
         </is>
       </c>
       <c r="E91" s="25" t="inlineStr">
@@ -4346,78 +4348,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="23" t="inlineStr">
-        <is>
-          <t>97859</t>
-        </is>
-      </c>
-      <c r="B92" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
-        </is>
-      </c>
-      <c r="C92" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D92" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E92" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F92" s="23" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
-      </c>
-      <c r="G92" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="25" t="inlineStr">
-        <is>
-          <t>97028</t>
-        </is>
-      </c>
-      <c r="B93" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C93" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D93" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E93" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F93" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G93" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" ht="60" customHeight="1">
-      <c r="A95" s="27" t="inlineStr">
+    <row r="93" ht="60" customHeight="1">
+      <c r="A93" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -4425,7 +4357,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A95:G95"/>
+    <mergeCell ref="A93:G93"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
